--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1383,6 +1383,618 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124784863</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skorvtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>776057</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7174839</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124784826</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skorvtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>776067</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7174828</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124784865</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skorvtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>776080</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7174816</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124784877</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98019</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrobotten, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>776053</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7174802</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124784864</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skorvtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>776051</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7174803</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124784926</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skorvtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>776063</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7174809</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784826</v>
+        <v>124784926</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,25 +1500,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776067</v>
+        <v>776063</v>
       </c>
       <c r="R9" t="n">
-        <v>7174828</v>
+        <v>7174809</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784864</v>
+        <v>124784826</v>
       </c>
       <c r="B12" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776051</v>
+        <v>776067</v>
       </c>
       <c r="R12" t="n">
-        <v>7174803</v>
+        <v>7174828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784926</v>
+        <v>124784864</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776063</v>
+        <v>776051</v>
       </c>
       <c r="R13" t="n">
-        <v>7174809</v>
+        <v>7174803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784863</v>
+        <v>124784877</v>
       </c>
       <c r="B8" t="n">
-        <v>98122</v>
+        <v>98019</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,34 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776057</v>
+        <v>776053</v>
       </c>
       <c r="R8" t="n">
-        <v>7174839</v>
+        <v>7174802</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784926</v>
+        <v>124784863</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,25 +1500,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776063</v>
+        <v>776057</v>
       </c>
       <c r="R9" t="n">
-        <v>7174809</v>
+        <v>7174839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784865</v>
+        <v>124784826</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776080</v>
+        <v>776067</v>
       </c>
       <c r="R10" t="n">
-        <v>7174816</v>
+        <v>7174828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784877</v>
+        <v>124784926</v>
       </c>
       <c r="B11" t="n">
-        <v>98019</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,38 +1704,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776053</v>
+        <v>776063</v>
       </c>
       <c r="R11" t="n">
-        <v>7174802</v>
+        <v>7174809</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784826</v>
+        <v>124784865</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776067</v>
+        <v>776080</v>
       </c>
       <c r="R12" t="n">
-        <v>7174828</v>
+        <v>7174816</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784877</v>
+        <v>124784863</v>
       </c>
       <c r="B8" t="n">
-        <v>98019</v>
+        <v>98122</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,34 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776053</v>
+        <v>776057</v>
       </c>
       <c r="R8" t="n">
-        <v>7174802</v>
+        <v>7174839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784863</v>
+        <v>124784864</v>
       </c>
       <c r="B9" t="n">
         <v>98122</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776057</v>
+        <v>776051</v>
       </c>
       <c r="R9" t="n">
-        <v>7174839</v>
+        <v>7174803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784826</v>
+        <v>124784865</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776067</v>
+        <v>776080</v>
       </c>
       <c r="R10" t="n">
-        <v>7174828</v>
+        <v>7174816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784865</v>
+        <v>124784826</v>
       </c>
       <c r="B12" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776080</v>
+        <v>776067</v>
       </c>
       <c r="R12" t="n">
-        <v>7174816</v>
+        <v>7174828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784864</v>
+        <v>124784877</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>98019</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,34 +1912,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776051</v>
+        <v>776053</v>
       </c>
       <c r="R13" t="n">
-        <v>7174803</v>
+        <v>7174802</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,7 +1386,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784863</v>
+        <v>124784865</v>
       </c>
       <c r="B8" t="n">
         <v>98122</v>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776057</v>
+        <v>776080</v>
       </c>
       <c r="R8" t="n">
-        <v>7174839</v>
+        <v>7174816</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784864</v>
+        <v>124784863</v>
       </c>
       <c r="B9" t="n">
         <v>98122</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776051</v>
+        <v>776057</v>
       </c>
       <c r="R9" t="n">
-        <v>7174803</v>
+        <v>7174839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784865</v>
+        <v>124784926</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1602,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776080</v>
+        <v>776063</v>
       </c>
       <c r="R10" t="n">
-        <v>7174816</v>
+        <v>7174809</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784926</v>
+        <v>124784864</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776063</v>
+        <v>776051</v>
       </c>
       <c r="R11" t="n">
-        <v>7174809</v>
+        <v>7174803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784865</v>
+        <v>124784826</v>
       </c>
       <c r="B8" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776080</v>
+        <v>776067</v>
       </c>
       <c r="R8" t="n">
-        <v>7174816</v>
+        <v>7174828</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784863</v>
+        <v>124784877</v>
       </c>
       <c r="B9" t="n">
-        <v>98122</v>
+        <v>98019</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,34 +1504,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776057</v>
+        <v>776053</v>
       </c>
       <c r="R9" t="n">
-        <v>7174839</v>
+        <v>7174802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784926</v>
+        <v>124784863</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1602,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776063</v>
+        <v>776057</v>
       </c>
       <c r="R10" t="n">
-        <v>7174809</v>
+        <v>7174839</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784864</v>
+        <v>124784865</v>
       </c>
       <c r="B11" t="n">
         <v>98122</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776051</v>
+        <v>776080</v>
       </c>
       <c r="R11" t="n">
-        <v>7174803</v>
+        <v>7174816</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784826</v>
+        <v>124784926</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,25 +1806,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776067</v>
+        <v>776063</v>
       </c>
       <c r="R12" t="n">
-        <v>7174828</v>
+        <v>7174809</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784877</v>
+        <v>124784864</v>
       </c>
       <c r="B13" t="n">
-        <v>98019</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,34 +1912,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776053</v>
+        <v>776051</v>
       </c>
       <c r="R13" t="n">
-        <v>7174802</v>
+        <v>7174803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784877</v>
+        <v>124784926</v>
       </c>
       <c r="B9" t="n">
-        <v>98019</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1500,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776053</v>
+        <v>776063</v>
       </c>
       <c r="R9" t="n">
-        <v>7174802</v>
+        <v>7174809</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784863</v>
+        <v>124784877</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>98019</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,34 +1606,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776057</v>
+        <v>776053</v>
       </c>
       <c r="R10" t="n">
-        <v>7174839</v>
+        <v>7174802</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784865</v>
+        <v>124784864</v>
       </c>
       <c r="B11" t="n">
         <v>98122</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776080</v>
+        <v>776051</v>
       </c>
       <c r="R11" t="n">
-        <v>7174816</v>
+        <v>7174803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784926</v>
+        <v>124784863</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,25 +1806,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776063</v>
+        <v>776057</v>
       </c>
       <c r="R12" t="n">
-        <v>7174809</v>
+        <v>7174839</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784864</v>
+        <v>124784865</v>
       </c>
       <c r="B13" t="n">
         <v>98122</v>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776051</v>
+        <v>776080</v>
       </c>
       <c r="R13" t="n">
-        <v>7174803</v>
+        <v>7174816</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784826</v>
+        <v>124784926</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776067</v>
+        <v>776063</v>
       </c>
       <c r="R8" t="n">
-        <v>7174828</v>
+        <v>7174809</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784926</v>
+        <v>124784877</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98019</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1500,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776063</v>
+        <v>776053</v>
       </c>
       <c r="R9" t="n">
-        <v>7174809</v>
+        <v>7174802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784877</v>
+        <v>124784826</v>
       </c>
       <c r="B10" t="n">
-        <v>98019</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,34 +1606,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223591</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776053</v>
+        <v>776067</v>
       </c>
       <c r="R10" t="n">
-        <v>7174802</v>
+        <v>7174828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784926</v>
+        <v>124784865</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776063</v>
+        <v>776080</v>
       </c>
       <c r="R8" t="n">
-        <v>7174809</v>
+        <v>7174816</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784865</v>
+        <v>124784926</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776080</v>
+        <v>776063</v>
       </c>
       <c r="R13" t="n">
-        <v>7174816</v>
+        <v>7174809</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784826</v>
+        <v>124784864</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776067</v>
+        <v>776051</v>
       </c>
       <c r="R10" t="n">
-        <v>7174828</v>
+        <v>7174803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784864</v>
+        <v>124784826</v>
       </c>
       <c r="B11" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776051</v>
+        <v>776067</v>
       </c>
       <c r="R11" t="n">
-        <v>7174803</v>
+        <v>7174828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784865</v>
+        <v>124784926</v>
       </c>
       <c r="B8" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776080</v>
+        <v>776063</v>
       </c>
       <c r="R8" t="n">
-        <v>7174816</v>
+        <v>7174809</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784826</v>
+        <v>124784865</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776067</v>
+        <v>776080</v>
       </c>
       <c r="R11" t="n">
-        <v>7174828</v>
+        <v>7174816</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784863</v>
+        <v>124784826</v>
       </c>
       <c r="B12" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776057</v>
+        <v>776067</v>
       </c>
       <c r="R12" t="n">
-        <v>7174839</v>
+        <v>7174828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784926</v>
+        <v>124784863</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776063</v>
+        <v>776057</v>
       </c>
       <c r="R13" t="n">
-        <v>7174809</v>
+        <v>7174839</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784926</v>
+        <v>124784863</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776063</v>
+        <v>776057</v>
       </c>
       <c r="R8" t="n">
-        <v>7174809</v>
+        <v>7174839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784877</v>
+        <v>124784926</v>
       </c>
       <c r="B9" t="n">
-        <v>98019</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1500,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776053</v>
+        <v>776063</v>
       </c>
       <c r="R9" t="n">
-        <v>7174802</v>
+        <v>7174809</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784864</v>
+        <v>124784865</v>
       </c>
       <c r="B10" t="n">
         <v>98122</v>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776051</v>
+        <v>776080</v>
       </c>
       <c r="R10" t="n">
-        <v>7174803</v>
+        <v>7174816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784865</v>
+        <v>124784877</v>
       </c>
       <c r="B11" t="n">
-        <v>98122</v>
+        <v>98019</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,34 +1708,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776080</v>
+        <v>776053</v>
       </c>
       <c r="R11" t="n">
-        <v>7174816</v>
+        <v>7174802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784826</v>
+        <v>124784864</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776067</v>
+        <v>776051</v>
       </c>
       <c r="R12" t="n">
-        <v>7174828</v>
+        <v>7174803</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784863</v>
+        <v>124784826</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776057</v>
+        <v>776067</v>
       </c>
       <c r="R13" t="n">
-        <v>7174839</v>
+        <v>7174828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784863</v>
+        <v>124784926</v>
       </c>
       <c r="B8" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776057</v>
+        <v>776063</v>
       </c>
       <c r="R8" t="n">
-        <v>7174839</v>
+        <v>7174809</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784926</v>
+        <v>124784877</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98019</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1500,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776063</v>
+        <v>776053</v>
       </c>
       <c r="R9" t="n">
-        <v>7174809</v>
+        <v>7174802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784865</v>
+        <v>124784864</v>
       </c>
       <c r="B10" t="n">
         <v>98122</v>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776080</v>
+        <v>776051</v>
       </c>
       <c r="R10" t="n">
-        <v>7174816</v>
+        <v>7174803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784877</v>
+        <v>124784865</v>
       </c>
       <c r="B11" t="n">
-        <v>98019</v>
+        <v>98122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,34 +1708,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776053</v>
+        <v>776080</v>
       </c>
       <c r="R11" t="n">
-        <v>7174802</v>
+        <v>7174816</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784864</v>
+        <v>124784826</v>
       </c>
       <c r="B12" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776051</v>
+        <v>776067</v>
       </c>
       <c r="R12" t="n">
-        <v>7174803</v>
+        <v>7174828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784826</v>
+        <v>124784863</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776067</v>
+        <v>776057</v>
       </c>
       <c r="R13" t="n">
-        <v>7174828</v>
+        <v>7174839</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784926</v>
+        <v>124784863</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776063</v>
+        <v>776057</v>
       </c>
       <c r="R8" t="n">
-        <v>7174809</v>
+        <v>7174839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784864</v>
+        <v>124784826</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776051</v>
+        <v>776067</v>
       </c>
       <c r="R10" t="n">
-        <v>7174803</v>
+        <v>7174828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784865</v>
+        <v>124784926</v>
       </c>
       <c r="B11" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776080</v>
+        <v>776063</v>
       </c>
       <c r="R11" t="n">
-        <v>7174816</v>
+        <v>7174809</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784826</v>
+        <v>124784864</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776067</v>
+        <v>776051</v>
       </c>
       <c r="R12" t="n">
-        <v>7174828</v>
+        <v>7174803</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784863</v>
+        <v>124784865</v>
       </c>
       <c r="B13" t="n">
         <v>98122</v>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776057</v>
+        <v>776080</v>
       </c>
       <c r="R13" t="n">
-        <v>7174839</v>
+        <v>7174816</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784863</v>
+        <v>124784826</v>
       </c>
       <c r="B8" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776057</v>
+        <v>776067</v>
       </c>
       <c r="R8" t="n">
-        <v>7174839</v>
+        <v>7174828</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784826</v>
+        <v>124784865</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776067</v>
+        <v>776080</v>
       </c>
       <c r="R10" t="n">
-        <v>7174828</v>
+        <v>7174816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784926</v>
+        <v>124784864</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776063</v>
+        <v>776051</v>
       </c>
       <c r="R11" t="n">
-        <v>7174809</v>
+        <v>7174803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784864</v>
+        <v>124784926</v>
       </c>
       <c r="B12" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,25 +1806,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776051</v>
+        <v>776063</v>
       </c>
       <c r="R12" t="n">
-        <v>7174803</v>
+        <v>7174809</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784865</v>
+        <v>124784863</v>
       </c>
       <c r="B13" t="n">
         <v>98122</v>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776080</v>
+        <v>776057</v>
       </c>
       <c r="R13" t="n">
-        <v>7174816</v>
+        <v>7174839</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784826</v>
+        <v>124784877</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>98187</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,34 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>223591</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776067</v>
+        <v>776053</v>
       </c>
       <c r="R8" t="n">
-        <v>7174828</v>
+        <v>7174802</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784877</v>
+        <v>124784926</v>
       </c>
       <c r="B9" t="n">
-        <v>98019</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1500,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776053</v>
+        <v>776063</v>
       </c>
       <c r="R9" t="n">
-        <v>7174802</v>
+        <v>7174809</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
         <v>124784865</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>98290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784864</v>
+        <v>124784826</v>
       </c>
       <c r="B11" t="n">
-        <v>98122</v>
+        <v>91131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776051</v>
+        <v>776067</v>
       </c>
       <c r="R11" t="n">
-        <v>7174803</v>
+        <v>7174828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784926</v>
+        <v>124784864</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>98290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,25 +1806,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776063</v>
+        <v>776051</v>
       </c>
       <c r="R12" t="n">
-        <v>7174809</v>
+        <v>7174803</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
         <v>124784863</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>98290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2019 artfynd.xlsx
+++ b/artfynd/A 31889-2019 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124784877</v>
+        <v>124784864</v>
       </c>
       <c r="B8" t="n">
-        <v>98187</v>
+        <v>98290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,34 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrobotten, Vb</t>
+          <t>Skorvtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776053</v>
+        <v>776051</v>
       </c>
       <c r="R8" t="n">
-        <v>7174802</v>
+        <v>7174803</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124784926</v>
+        <v>124784865</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>98290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,25 +1500,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776063</v>
+        <v>776080</v>
       </c>
       <c r="R9" t="n">
-        <v>7174809</v>
+        <v>7174816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124784865</v>
+        <v>124784926</v>
       </c>
       <c r="B10" t="n">
-        <v>98290</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1602,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776080</v>
+        <v>776063</v>
       </c>
       <c r="R10" t="n">
-        <v>7174816</v>
+        <v>7174809</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124784826</v>
+        <v>124784863</v>
       </c>
       <c r="B11" t="n">
-        <v>91131</v>
+        <v>98290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776067</v>
+        <v>776057</v>
       </c>
       <c r="R11" t="n">
-        <v>7174828</v>
+        <v>7174839</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124784864</v>
+        <v>124784826</v>
       </c>
       <c r="B12" t="n">
-        <v>98290</v>
+        <v>91131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776051</v>
+        <v>776067</v>
       </c>
       <c r="R12" t="n">
-        <v>7174803</v>
+        <v>7174828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124784863</v>
+        <v>124784877</v>
       </c>
       <c r="B13" t="n">
-        <v>98290</v>
+        <v>98187</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,34 +1912,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skorvtjärnen, Vb</t>
+          <t>Norrobotten, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776057</v>
+        <v>776053</v>
       </c>
       <c r="R13" t="n">
-        <v>7174839</v>
+        <v>7174802</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
